--- a/release/templates/combo_template_all_characters_simple.xlsx
+++ b/release/templates/combo_template_all_characters_simple.xlsx
@@ -8,41 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Edit\Documents\SF6_Lab\release\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F204C4-E829-4078-A02B-1917ACBF1605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2928637-ABA3-4D7F-88FF-2E4335C7F740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aki" sheetId="1" r:id="rId1"/>
     <sheet name="alex" sheetId="2" r:id="rId2"/>
-    <sheet name="blanka" sheetId="3" r:id="rId3"/>
-    <sheet name="cammy" sheetId="4" r:id="rId4"/>
-    <sheet name="chunli" sheetId="5" r:id="rId5"/>
-    <sheet name="cviper" sheetId="6" r:id="rId6"/>
-    <sheet name="deejay" sheetId="7" r:id="rId7"/>
-    <sheet name="dhalsim" sheetId="8" r:id="rId8"/>
-    <sheet name="ed" sheetId="9" r:id="rId9"/>
-    <sheet name="ehonda" sheetId="10" r:id="rId10"/>
-    <sheet name="elena" sheetId="11" r:id="rId11"/>
-    <sheet name="gouki_akuma" sheetId="12" r:id="rId12"/>
-    <sheet name="guile" sheetId="13" r:id="rId13"/>
-    <sheet name="Ingrid" sheetId="30" r:id="rId14"/>
-    <sheet name="jamie" sheetId="14" r:id="rId15"/>
-    <sheet name="jp" sheetId="15" r:id="rId16"/>
-    <sheet name="juri" sheetId="16" r:id="rId17"/>
-    <sheet name="ken" sheetId="17" r:id="rId18"/>
-    <sheet name="kimberly" sheetId="18" r:id="rId19"/>
-    <sheet name="lily" sheetId="19" r:id="rId20"/>
-    <sheet name="luke" sheetId="20" r:id="rId21"/>
-    <sheet name="mai" sheetId="21" r:id="rId22"/>
-    <sheet name="manon" sheetId="22" r:id="rId23"/>
-    <sheet name="marisa" sheetId="23" r:id="rId24"/>
-    <sheet name="rashid" sheetId="24" r:id="rId25"/>
-    <sheet name="ryu" sheetId="25" r:id="rId26"/>
-    <sheet name="sagat" sheetId="26" r:id="rId27"/>
-    <sheet name="terry" sheetId="27" r:id="rId28"/>
-    <sheet name="vega_mbison" sheetId="28" r:id="rId29"/>
-    <sheet name="zangief" sheetId="29" r:id="rId30"/>
+    <sheet name="arjun" sheetId="31" r:id="rId3"/>
+    <sheet name="blanka" sheetId="3" r:id="rId4"/>
+    <sheet name="cammy" sheetId="4" r:id="rId5"/>
+    <sheet name="chunli" sheetId="5" r:id="rId6"/>
+    <sheet name="cviper" sheetId="6" r:id="rId7"/>
+    <sheet name="deejay" sheetId="7" r:id="rId8"/>
+    <sheet name="dhalsim" sheetId="8" r:id="rId9"/>
+    <sheet name="ed" sheetId="9" r:id="rId10"/>
+    <sheet name="ehonda" sheetId="10" r:id="rId11"/>
+    <sheet name="elena" sheetId="11" r:id="rId12"/>
+    <sheet name="gouki_akuma" sheetId="12" r:id="rId13"/>
+    <sheet name="guile" sheetId="13" r:id="rId14"/>
+    <sheet name="ingrid" sheetId="30" r:id="rId15"/>
+    <sheet name="jamie" sheetId="14" r:id="rId16"/>
+    <sheet name="jp" sheetId="15" r:id="rId17"/>
+    <sheet name="juri" sheetId="16" r:id="rId18"/>
+    <sheet name="ken" sheetId="17" r:id="rId19"/>
+    <sheet name="kimberly" sheetId="18" r:id="rId20"/>
+    <sheet name="lily" sheetId="19" r:id="rId21"/>
+    <sheet name="luke" sheetId="20" r:id="rId22"/>
+    <sheet name="mai" sheetId="21" r:id="rId23"/>
+    <sheet name="manon" sheetId="22" r:id="rId24"/>
+    <sheet name="marisa" sheetId="23" r:id="rId25"/>
+    <sheet name="rashid" sheetId="24" r:id="rId26"/>
+    <sheet name="ryu" sheetId="25" r:id="rId27"/>
+    <sheet name="sagat" sheetId="26" r:id="rId28"/>
+    <sheet name="terry" sheetId="27" r:id="rId29"/>
+    <sheet name="vega_mbison" sheetId="28" r:id="rId30"/>
+    <sheet name="yasmine" sheetId="32" r:id="rId31"/>
+    <sheet name="zangief" sheetId="29" r:id="rId32"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="4">
   <si>
     <t>Command</t>
   </si>
@@ -652,6 +654,155 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -800,7 +951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -949,7 +1100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1098,7 +1249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1247,7 +1398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4674CE55-C851-4E78-9471-F0341653D8CF}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1396,7 +1547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1545,7 +1696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1694,7 +1845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1843,157 +1994,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="52.7265625" customWidth="1"/>
-    <col min="2" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2291,6 +2293,155 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2439,7 +2590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2588,7 +2739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2737,7 +2888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2886,7 +3037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3035,7 +3186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3184,7 +3335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3333,7 +3484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3482,7 +3633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3631,7 +3782,156 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12B733B-F05B-4EE9-A3F3-ECC40FFE886C}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3780,7 +4080,305 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59D70F2-22AA-4263-9FEA-7FF193CD1A93}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.7265625" customWidth="1"/>
+    <col min="2" max="3" width="16.7265625" customWidth="1"/>
+    <col min="4" max="4" width="28.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3929,156 +4527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="52.7265625" customWidth="1"/>
-    <col min="2" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4227,7 +4676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4376,7 +4825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4525,7 +4974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4674,7 +5123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4821,153 +5270,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="52.7265625" customWidth="1"/>
-    <col min="2" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="28.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>